--- a/03_Outputs/San_Juan/05_Economia/economia.xlsx
+++ b/03_Outputs/San_Juan/05_Economia/economia.xlsx
@@ -9290,10 +9290,8 @@
       <c r="F21" s="118">
         <v>94.5071801179086</v>
       </c>
-      <c r="G21" s="120" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G21" s="120">
+        <v>0.00728332707735775</v>
       </c>
       <c r="H21" s="122">
         <v>3.76044977809165</v>
@@ -9354,7 +9352,7 @@
         <v>441.996422036508</v>
       </c>
       <c r="G22" s="121">
-        <v>0.240683604889276</v>
+        <v>0.247966931966634</v>
       </c>
       <c r="H22" s="123">
         <v>112.86767453273</v>
@@ -11367,10 +11365,8 @@
       <c r="F56" s="118">
         <v>96.8089113780746</v>
       </c>
-      <c r="G56" s="120" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G56" s="120">
+        <v>0.00766482793923947</v>
       </c>
       <c r="H56" s="122">
         <v>6.96532158990451</v>
@@ -11431,7 +11427,7 @@
         <v>398.579841467372</v>
       </c>
       <c r="G57" s="121">
-        <v>5.3728164215901</v>
+        <v>5.38048124952934</v>
       </c>
       <c r="H57" s="123">
         <v>47.6146158795269</v>
